--- a/SType2.xlsx
+++ b/SType2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-PADAGIMO-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A41342C-B3F5-4A60-AB0E-0E5127761BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{1A41342C-B3F5-4A60-AB0E-0E5127761BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E66C01E1-AD95-4B85-A0FE-B76ED57678DB}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B0285223-0237-4445-BB2D-68F96528C948}"/>
   </bookViews>
@@ -18,28 +18,27 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
-    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
     <definedName name="Chart_Sektor_name">OFFSET([1]Industri_Unggulan!$B$8,1,1,[1]g!$E$3,1)</definedName>
     <definedName name="Chart_Sektor_x">OFFSET([1]Industri_Unggulan!$F$8,1,1,[1]g!$E$3,1)</definedName>
     <definedName name="Chart_Sektor_y">OFFSET([1]Industri_Unggulan!$E$8,1,1,[1]g!$E$3,1)</definedName>
     <definedName name="cwww10">#REF!</definedName>
-    <definedName name="Industri">[3]K.Supply!$P$2:$P$96</definedName>
-    <definedName name="Kategori">[3]Sheet1!$U$2:$U$18</definedName>
-    <definedName name="Nama_KabKota">[3]Sheet2!$F$2:$F$40</definedName>
-    <definedName name="NamaTabel">OFFSET(INDIRECT("S3R!$"&amp;[3]S2LP!$G$2&amp;"$6"),0,0,1,[3]S2LP!$G$1)</definedName>
+    <definedName name="Industri">[2]K.Supply!$P$2:$P$96</definedName>
+    <definedName name="Kategori">[2]Sheet1!$U$2:$U$18</definedName>
+    <definedName name="Nama_KabKota">[2]Sheet2!$F$2:$F$40</definedName>
+    <definedName name="NamaTabel">OFFSET(INDIRECT("S3R!$"&amp;[2]S2LP!$G$2&amp;"$6"),0,0,1,[2]S2LP!$G$1)</definedName>
     <definedName name="NamaTabelImplisit">OFFSET(INDIRECT("S3R!$"&amp;#REF!&amp;"$6"),0,0,1,#REF!)</definedName>
-    <definedName name="Produk">[3]K.Supply!$T$2:$T$76</definedName>
-    <definedName name="Tabel">OFFSET(INDIRECT("S3R!$"&amp;[3]S2LP!$G$2&amp;"$"&amp;[3]S2LP!$H$1),0,0,1,[3]S2LP!$G$1)</definedName>
+    <definedName name="Produk">[2]K.Supply!$T$2:$T$76</definedName>
+    <definedName name="Tabel">OFFSET(INDIRECT("S3R!$"&amp;[2]S2LP!$G$2&amp;"$"&amp;[2]S2LP!$H$1),0,0,1,[2]S2LP!$G$1)</definedName>
     <definedName name="TabelImplisit">OFFSET(INDIRECT("S3R!$"&amp;#REF!&amp;"$"&amp;#REF!),0,0,1,#REF!)</definedName>
-    <definedName name="TabelKab">OFFSET(INDIRECT("S3R!$"&amp;[3]S2LP!$G$2&amp;"$"&amp;[3]S2LP!$H$2),0,0,1,[3]S2LP!$G$1)</definedName>
+    <definedName name="TabelKab">OFFSET(INDIRECT("S3R!$"&amp;[2]S2LP!$G$2&amp;"$"&amp;[2]S2LP!$H$2),0,0,1,[2]S2LP!$G$1)</definedName>
     <definedName name="TabelKabImplisit">OFFSET(INDIRECT("S3R!$"&amp;#REF!&amp;"$"&amp;#REF!),0,0,1,#REF!)</definedName>
-    <definedName name="TabelKabTotal">OFFSET(INDIRECT("S3R!$"&amp;[3]S2LP!$G$2&amp;"$170"),0,0,1,[3]S2LP!$G$1)</definedName>
+    <definedName name="TabelKabTotal">OFFSET(INDIRECT("S3R!$"&amp;[2]S2LP!$G$2&amp;"$170"),0,0,1,[2]S2LP!$G$1)</definedName>
     <definedName name="TabelKabTotalImplisit">OFFSET(INDIRECT("S3R!$"&amp;#REF!&amp;"$293"),0,0,1,#REF!)</definedName>
-    <definedName name="TabelTotal">OFFSET(INDIRECT("S3R!$"&amp;[3]S2LP!$G$2&amp;"$169"),0,0,1,[3]S2LP!$G$1)</definedName>
+    <definedName name="TabelTotal">OFFSET(INDIRECT("S3R!$"&amp;[2]S2LP!$G$2&amp;"$169"),0,0,1,[2]S2LP!$G$1)</definedName>
     <definedName name="TabelTotalImplisit">OFFSET(INDIRECT("S3R!$"&amp;#REF!&amp;"$292"),0,0,1,#REF!)</definedName>
-    <definedName name="Tahun">[3]Sheet1!$A$2:$A$18</definedName>
+    <definedName name="Tahun">[2]Sheet1!$A$2:$A$18</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,10 +61,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -264,56 +259,6 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="IO_2024 (RAW)"/>
-      <sheetName val="Tenaga Kerja"/>
-      <sheetName val="IO-2024 (CEK)"/>
-      <sheetName val="input baris R"/>
-      <sheetName val="PDRB_Kabupaten"/>
-      <sheetName val="PDRB_Padagimo"/>
-      <sheetName val="io"/>
-      <sheetName val="DeskripsiSektor"/>
-      <sheetName val="BAU_Lahan"/>
-      <sheetName val="LAS_Lahan"/>
-      <sheetName val="LDC"/>
-      <sheetName val="SType1"/>
-      <sheetName val="SType2"/>
-      <sheetName val="Stype3"/>
-      <sheetName val="ProyeksiPopulasi"/>
-      <sheetName val="populasiPenduduk"/>
-      <sheetName val="populasiPesisir"/>
-      <sheetName val="PendudukPesisir"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -835,13 +780,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6805BBD-9864-4868-9F2B-A463A77EC73A}">
-  <dimension ref="A1:Z62"/>
+  <dimension ref="A1:V62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="10" max="23" width="8.88671875" customWidth="1"/>
+    <col min="10" max="22" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>2024</v>
       </c>
@@ -908,20 +853,8 @@
       <c r="V1">
         <v>2045</v>
       </c>
-      <c r="W1">
-        <v>2046</v>
-      </c>
-      <c r="X1">
-        <v>2047</v>
-      </c>
-      <c r="Y1">
-        <v>2048</v>
-      </c>
-      <c r="Z1">
-        <v>2049</v>
-      </c>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -988,20 +921,8 @@
       <c r="V2">
         <v>5.9565217391304347E-2</v>
       </c>
-      <c r="W2">
-        <v>6.217391304347826E-2</v>
-      </c>
-      <c r="X2">
-        <v>6.4782608695652166E-2</v>
-      </c>
-      <c r="Y2">
-        <v>6.7391304347826086E-2</v>
-      </c>
-      <c r="Z2">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>0</v>
       </c>
@@ -1068,20 +989,8 @@
       <c r="V3">
         <v>5.8571428571428573E-2</v>
       </c>
-      <c r="W3">
-        <v>6.142857142857143E-2</v>
-      </c>
-      <c r="X3">
-        <v>6.4285714285714279E-2</v>
-      </c>
-      <c r="Y3">
-        <v>6.7142857142857143E-2</v>
-      </c>
-      <c r="Z3">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>0</v>
       </c>
@@ -1148,20 +1057,8 @@
       <c r="V4">
         <v>8.2857142857142865E-2</v>
       </c>
-      <c r="W4">
-        <v>8.7142857142857147E-2</v>
-      </c>
-      <c r="X4">
-        <v>9.1428571428571428E-2</v>
-      </c>
-      <c r="Y4">
-        <v>9.5714285714285724E-2</v>
-      </c>
-      <c r="Z4">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>0</v>
       </c>
@@ -1228,20 +1125,8 @@
       <c r="V5">
         <v>7.4761904761904752E-2</v>
       </c>
-      <c r="W5">
-        <v>7.857142857142857E-2</v>
-      </c>
-      <c r="X5">
-        <v>8.2380952380952388E-2</v>
-      </c>
-      <c r="Y5">
-        <v>8.6190476190476178E-2</v>
-      </c>
-      <c r="Z5">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>0</v>
       </c>
@@ -1308,20 +1193,8 @@
       <c r="V6">
         <v>7.4761904761904752E-2</v>
       </c>
-      <c r="W6">
-        <v>7.857142857142857E-2</v>
-      </c>
-      <c r="X6">
-        <v>8.2380952380952388E-2</v>
-      </c>
-      <c r="Y6">
-        <v>8.6190476190476178E-2</v>
-      </c>
-      <c r="Z6">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>0</v>
       </c>
@@ -1388,20 +1261,8 @@
       <c r="V7">
         <v>7.4761904761904752E-2</v>
       </c>
-      <c r="W7">
-        <v>7.857142857142857E-2</v>
-      </c>
-      <c r="X7">
-        <v>8.2380952380952388E-2</v>
-      </c>
-      <c r="Y7">
-        <v>8.6190476190476178E-2</v>
-      </c>
-      <c r="Z7">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>0</v>
       </c>
@@ -1468,20 +1329,8 @@
       <c r="V8">
         <v>9.5110107284020334E-2</v>
       </c>
-      <c r="W8">
-        <v>0.10058159232072278</v>
-      </c>
-      <c r="X8">
-        <v>0.1060530773574252</v>
-      </c>
-      <c r="Y8">
-        <v>0.11152456239412764</v>
-      </c>
-      <c r="Z8">
-        <v>0.11699604743083006</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>0</v>
       </c>
@@ -1548,20 +1397,8 @@
       <c r="V9">
         <v>0.13411764705882354</v>
       </c>
-      <c r="W9">
-        <v>0.14058823529411765</v>
-      </c>
-      <c r="X9">
-        <v>0.14705882352941177</v>
-      </c>
-      <c r="Y9">
-        <v>0.15352941176470589</v>
-      </c>
-      <c r="Z9">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>0</v>
       </c>
@@ -1628,20 +1465,8 @@
       <c r="V10">
         <v>8.4347826086956512E-2</v>
       </c>
-      <c r="W10">
-        <v>8.8260869565217392E-2</v>
-      </c>
-      <c r="X10">
-        <v>9.2173913043478245E-2</v>
-      </c>
-      <c r="Y10">
-        <v>9.6086956521739125E-2</v>
-      </c>
-      <c r="Z10">
-        <v>9.9999999999999978E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>0</v>
       </c>
@@ -1708,20 +1533,8 @@
       <c r="V11">
         <v>0.25238095238095237</v>
       </c>
-      <c r="W11">
-        <v>0.26428571428571423</v>
-      </c>
-      <c r="X11">
-        <v>0.27619047619047621</v>
-      </c>
-      <c r="Y11">
-        <v>0.28809523809523807</v>
-      </c>
-      <c r="Z11">
-        <v>0.29999999999999993</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>0</v>
       </c>
@@ -1788,20 +1601,8 @@
       <c r="V12">
         <v>0.25238095238095237</v>
       </c>
-      <c r="W12">
-        <v>0.26428571428571423</v>
-      </c>
-      <c r="X12">
-        <v>0.27619047619047621</v>
-      </c>
-      <c r="Y12">
-        <v>0.28809523809523807</v>
-      </c>
-      <c r="Z12">
-        <v>0.29999999999999993</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>0</v>
       </c>
@@ -1868,20 +1669,8 @@
       <c r="V13">
         <v>0.1647058823529412</v>
       </c>
-      <c r="W13">
-        <v>0.17352941176470593</v>
-      </c>
-      <c r="X13">
-        <v>0.18235294117647063</v>
-      </c>
-      <c r="Y13">
-        <v>0.19117647058823534</v>
-      </c>
-      <c r="Z13">
-        <v>0.20000000000000007</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>0</v>
       </c>
@@ -1948,20 +1737,8 @@
       <c r="V14">
         <v>0.15529411764705886</v>
       </c>
-      <c r="W14">
-        <v>0.16647058823529418</v>
-      </c>
-      <c r="X14">
-        <v>0.17764705882352946</v>
-      </c>
-      <c r="Y14">
-        <v>0.18882352941176475</v>
-      </c>
-      <c r="Z14">
-        <v>0.20000000000000007</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>0</v>
       </c>
@@ -2028,20 +1805,8 @@
       <c r="V15" s="1">
         <v>0</v>
       </c>
-      <c r="W15" s="1">
-        <v>0</v>
-      </c>
-      <c r="X15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>0</v>
       </c>
@@ -2108,20 +1873,8 @@
       <c r="V16" s="1">
         <v>0</v>
       </c>
-      <c r="W16" s="1">
-        <v>0</v>
-      </c>
-      <c r="X16" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>0</v>
       </c>
@@ -2188,20 +1941,8 @@
       <c r="V17" s="1">
         <v>0</v>
       </c>
-      <c r="W17" s="1">
-        <v>0</v>
-      </c>
-      <c r="X17" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>0</v>
       </c>
@@ -2268,20 +2009,8 @@
       <c r="V18">
         <v>0.17142857142857146</v>
       </c>
-      <c r="W18">
-        <v>0.1785714285714286</v>
-      </c>
-      <c r="X18">
-        <v>0.18571428571428575</v>
-      </c>
-      <c r="Y18">
-        <v>0.19285714285714289</v>
-      </c>
-      <c r="Z18">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>0</v>
       </c>
@@ -2348,20 +2077,8 @@
       <c r="V19">
         <v>0.21714285714285714</v>
       </c>
-      <c r="W19">
-        <v>0.23785714285714285</v>
-      </c>
-      <c r="X19">
-        <v>0.25857142857142856</v>
-      </c>
-      <c r="Y19">
-        <v>0.27928571428571425</v>
-      </c>
-      <c r="Z19">
-        <v>0.30000000000000004</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>0</v>
       </c>
@@ -2428,20 +2145,8 @@
       <c r="V20" s="1">
         <v>0</v>
       </c>
-      <c r="W20" s="1">
-        <v>0</v>
-      </c>
-      <c r="X20" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>0</v>
       </c>
@@ -2508,20 +2213,8 @@
       <c r="V21" s="1">
         <v>0</v>
       </c>
-      <c r="W21" s="1">
-        <v>0</v>
-      </c>
-      <c r="X21" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>0</v>
       </c>
@@ -2588,20 +2281,8 @@
       <c r="V22" s="1">
         <v>0</v>
       </c>
-      <c r="W22" s="1">
-        <v>0</v>
-      </c>
-      <c r="X22" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>0</v>
       </c>
@@ -2668,20 +2349,8 @@
       <c r="V23">
         <v>0.14571428571428574</v>
       </c>
-      <c r="W23">
-        <v>0.15928571428571431</v>
-      </c>
-      <c r="X23">
-        <v>0.17285714285714288</v>
-      </c>
-      <c r="Y23">
-        <v>0.18642857142857147</v>
-      </c>
-      <c r="Z23">
-        <v>0.20000000000000004</v>
-      </c>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>0</v>
       </c>
@@ -2748,20 +2417,8 @@
       <c r="V24" s="1">
         <v>0</v>
       </c>
-      <c r="W24" s="1">
-        <v>0</v>
-      </c>
-      <c r="X24" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>0</v>
       </c>
@@ -2828,20 +2485,8 @@
       <c r="V25" s="1">
         <v>0</v>
       </c>
-      <c r="W25" s="1">
-        <v>0</v>
-      </c>
-      <c r="X25" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>0</v>
       </c>
@@ -2908,20 +2553,8 @@
       <c r="V26" s="1">
         <v>0</v>
       </c>
-      <c r="W26" s="1">
-        <v>0</v>
-      </c>
-      <c r="X26" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>0</v>
       </c>
@@ -2988,20 +2621,8 @@
       <c r="V27" s="1">
         <v>0</v>
       </c>
-      <c r="W27" s="1">
-        <v>0</v>
-      </c>
-      <c r="X27" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>0</v>
       </c>
@@ -3068,20 +2689,8 @@
       <c r="V28" s="1">
         <v>0</v>
       </c>
-      <c r="W28" s="1">
-        <v>0</v>
-      </c>
-      <c r="X28" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>0</v>
       </c>
@@ -3148,20 +2757,8 @@
       <c r="V29" s="1">
         <v>0</v>
       </c>
-      <c r="W29" s="1">
-        <v>0</v>
-      </c>
-      <c r="X29" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>0</v>
       </c>
@@ -3228,20 +2825,8 @@
       <c r="V30" s="1">
         <v>0</v>
       </c>
-      <c r="W30" s="1">
-        <v>0</v>
-      </c>
-      <c r="X30" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>0</v>
       </c>
@@ -3308,20 +2893,8 @@
       <c r="V31" s="1">
         <v>0</v>
       </c>
-      <c r="W31" s="1">
-        <v>0</v>
-      </c>
-      <c r="X31" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>0</v>
       </c>
@@ -3388,20 +2961,8 @@
       <c r="V32" s="1">
         <v>0</v>
       </c>
-      <c r="W32" s="1">
-        <v>0</v>
-      </c>
-      <c r="X32" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>0</v>
       </c>
@@ -3468,20 +3029,8 @@
       <c r="V33" s="1">
         <v>0</v>
       </c>
-      <c r="W33" s="1">
-        <v>0</v>
-      </c>
-      <c r="X33" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>0</v>
       </c>
@@ -3548,20 +3097,8 @@
       <c r="V34" s="1">
         <v>0</v>
       </c>
-      <c r="W34" s="1">
-        <v>0</v>
-      </c>
-      <c r="X34" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>0</v>
       </c>
@@ -3628,20 +3165,8 @@
       <c r="V35" s="1">
         <v>0</v>
       </c>
-      <c r="W35" s="1">
-        <v>0</v>
-      </c>
-      <c r="X35" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>0</v>
       </c>
@@ -3708,20 +3233,8 @@
       <c r="V36" s="1">
         <v>0</v>
       </c>
-      <c r="W36" s="1">
-        <v>0</v>
-      </c>
-      <c r="X36" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z36" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>0</v>
       </c>
@@ -3788,20 +3301,8 @@
       <c r="V37" s="1">
         <v>0</v>
       </c>
-      <c r="W37" s="1">
-        <v>0</v>
-      </c>
-      <c r="X37" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z37" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>0</v>
       </c>
@@ -3868,20 +3369,8 @@
       <c r="V38" s="1">
         <v>0</v>
       </c>
-      <c r="W38" s="1">
-        <v>0</v>
-      </c>
-      <c r="X38" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y38" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>0</v>
       </c>
@@ -3948,20 +3437,8 @@
       <c r="V39" s="1">
         <v>0</v>
       </c>
-      <c r="W39" s="1">
-        <v>0</v>
-      </c>
-      <c r="X39" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y39" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z39" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>0</v>
       </c>
@@ -4028,20 +3505,8 @@
       <c r="V40" s="1">
         <v>0</v>
       </c>
-      <c r="W40" s="1">
-        <v>0</v>
-      </c>
-      <c r="X40" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y40" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z40" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>0</v>
       </c>
@@ -4108,20 +3573,8 @@
       <c r="V41" s="1">
         <v>0</v>
       </c>
-      <c r="W41" s="1">
-        <v>0</v>
-      </c>
-      <c r="X41" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>0</v>
       </c>
@@ -4188,20 +3641,8 @@
       <c r="V42" s="1">
         <v>0</v>
       </c>
-      <c r="W42" s="1">
-        <v>0</v>
-      </c>
-      <c r="X42" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>0</v>
       </c>
@@ -4268,20 +3709,8 @@
       <c r="V43" s="1">
         <v>0</v>
       </c>
-      <c r="W43" s="1">
-        <v>0</v>
-      </c>
-      <c r="X43" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>0</v>
       </c>
@@ -4348,20 +3777,8 @@
       <c r="V44" s="1">
         <v>0</v>
       </c>
-      <c r="W44" s="1">
-        <v>0</v>
-      </c>
-      <c r="X44" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>0</v>
       </c>
@@ -4428,20 +3845,8 @@
       <c r="V45" s="1">
         <v>0</v>
       </c>
-      <c r="W45" s="1">
-        <v>0</v>
-      </c>
-      <c r="X45" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z45" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>0</v>
       </c>
@@ -4508,20 +3913,8 @@
       <c r="V46" s="1">
         <v>0</v>
       </c>
-      <c r="W46" s="1">
-        <v>0</v>
-      </c>
-      <c r="X46" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z46" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>0</v>
       </c>
@@ -4588,20 +3981,8 @@
       <c r="V47" s="1">
         <v>0</v>
       </c>
-      <c r="W47" s="1">
-        <v>0</v>
-      </c>
-      <c r="X47" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y47" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z47" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>0</v>
       </c>
@@ -4668,20 +4049,8 @@
       <c r="V48" s="1">
         <v>0</v>
       </c>
-      <c r="W48" s="1">
-        <v>0</v>
-      </c>
-      <c r="X48" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y48" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z48" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>0</v>
       </c>
@@ -4748,20 +4117,8 @@
       <c r="V49" s="1">
         <v>0</v>
       </c>
-      <c r="W49" s="1">
-        <v>0</v>
-      </c>
-      <c r="X49" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y49" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z49" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>0</v>
       </c>
@@ -4828,20 +4185,8 @@
       <c r="V50" s="1">
         <v>0</v>
       </c>
-      <c r="W50" s="1">
-        <v>0</v>
-      </c>
-      <c r="X50" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y50" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z50" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>0</v>
       </c>
@@ -4908,20 +4253,8 @@
       <c r="V51" s="1">
         <v>0</v>
       </c>
-      <c r="W51" s="1">
-        <v>0</v>
-      </c>
-      <c r="X51" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y51" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z51" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>0</v>
       </c>
@@ -4988,20 +4321,8 @@
       <c r="V52" s="1">
         <v>0</v>
       </c>
-      <c r="W52" s="1">
-        <v>0</v>
-      </c>
-      <c r="X52" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z52" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>0</v>
       </c>
@@ -5068,20 +4389,8 @@
       <c r="V53" s="1">
         <v>0</v>
       </c>
-      <c r="W53" s="1">
-        <v>0</v>
-      </c>
-      <c r="X53" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y53" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z53" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>0</v>
       </c>
@@ -5148,20 +4457,8 @@
       <c r="V54" s="1">
         <v>0</v>
       </c>
-      <c r="W54" s="1">
-        <v>0</v>
-      </c>
-      <c r="X54" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y54" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z54" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>0</v>
       </c>
@@ -5228,20 +4525,8 @@
       <c r="V55" s="1">
         <v>0</v>
       </c>
-      <c r="W55" s="1">
-        <v>0</v>
-      </c>
-      <c r="X55" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y55" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z55" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>0</v>
       </c>
@@ -5308,20 +4593,8 @@
       <c r="V56" s="1">
         <v>0</v>
       </c>
-      <c r="W56" s="1">
-        <v>0</v>
-      </c>
-      <c r="X56" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y56" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z56" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>0</v>
       </c>
@@ -5388,20 +4661,8 @@
       <c r="V57" s="1">
         <v>0</v>
       </c>
-      <c r="W57" s="1">
-        <v>0</v>
-      </c>
-      <c r="X57" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>0</v>
       </c>
@@ -5468,20 +4729,8 @@
       <c r="V58" s="1">
         <v>0</v>
       </c>
-      <c r="W58" s="1">
-        <v>0</v>
-      </c>
-      <c r="X58" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>0</v>
       </c>
@@ -5548,20 +4797,8 @@
       <c r="V59" s="1">
         <v>0</v>
       </c>
-      <c r="W59" s="1">
-        <v>0</v>
-      </c>
-      <c r="X59" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y59" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z59" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>0</v>
       </c>
@@ -5628,20 +4865,8 @@
       <c r="V60" s="1">
         <v>0</v>
       </c>
-      <c r="W60" s="1">
-        <v>0</v>
-      </c>
-      <c r="X60" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y60" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z60" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>0</v>
       </c>
@@ -5708,20 +4933,8 @@
       <c r="V61" s="1">
         <v>0</v>
       </c>
-      <c r="W61" s="1">
-        <v>0</v>
-      </c>
-      <c r="X61" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>0</v>
       </c>
@@ -5786,18 +4999,6 @@
         <v>0</v>
       </c>
       <c r="V62" s="1">
-        <v>0</v>
-      </c>
-      <c r="W62" s="1">
-        <v>0</v>
-      </c>
-      <c r="X62" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y62" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="1">
         <v>0</v>
       </c>
     </row>

--- a/SType2.xlsx
+++ b/SType2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-PADAGIMO-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{1A41342C-B3F5-4A60-AB0E-0E5127761BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E66C01E1-AD95-4B85-A0FE-B76ED57678DB}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{1A41342C-B3F5-4A60-AB0E-0E5127761BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01C40B24-DBFB-467B-AAB6-E287C2A9EDFB}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B0285223-0237-4445-BB2D-68F96528C948}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{B0285223-0237-4445-BB2D-68F96528C948}"/>
   </bookViews>
   <sheets>
     <sheet name="SType2" sheetId="1" r:id="rId1"/>
@@ -862,64 +862,64 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>9.999999999999995E-3</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1.2608695652173908E-2</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1.5217391304347822E-2</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>1.7826086956521735E-2</v>
+        <v>9.9999999999999985E-3</v>
       </c>
       <c r="G2">
-        <v>2.0434782608695648E-2</v>
+        <v>1.6370418594538257E-2</v>
       </c>
       <c r="H2">
-        <v>2.3043478260869561E-2</v>
+        <v>2.2740837189076511E-2</v>
       </c>
       <c r="I2">
-        <v>2.5652173913043474E-2</v>
+        <v>2.9111255783614769E-2</v>
       </c>
       <c r="J2">
-        <v>2.8260869565217388E-2</v>
+        <v>3.5481674378153027E-2</v>
       </c>
       <c r="K2">
-        <v>3.0869565217391301E-2</v>
+        <v>4.1852092972691282E-2</v>
       </c>
       <c r="L2">
-        <v>3.3478260869565214E-2</v>
+        <v>4.8222511567229544E-2</v>
       </c>
       <c r="M2">
-        <v>3.6086956521739127E-2</v>
+        <v>5.4592930161767798E-2</v>
       </c>
       <c r="N2">
-        <v>3.8695652173913041E-2</v>
+        <v>6.0963348756306053E-2</v>
       </c>
       <c r="O2">
-        <v>4.1304347826086954E-2</v>
+        <v>6.7333767350844315E-2</v>
       </c>
       <c r="P2">
-        <v>4.3913043478260867E-2</v>
+        <v>7.3704185945382569E-2</v>
       </c>
       <c r="Q2">
-        <v>4.652173913043478E-2</v>
+        <v>8.0074604539920824E-2</v>
       </c>
       <c r="R2">
-        <v>4.9130434782608694E-2</v>
+        <v>8.6445023134459079E-2</v>
       </c>
       <c r="S2">
-        <v>5.1739130434782607E-2</v>
+        <v>9.2815441728997347E-2</v>
       </c>
       <c r="T2">
-        <v>5.434782608695652E-2</v>
+        <v>9.9185860323535602E-2</v>
       </c>
       <c r="U2">
-        <v>5.6956521739130433E-2</v>
+        <v>0.10555627891807386</v>
       </c>
       <c r="V2">
-        <v>5.9565217391304347E-2</v>
+        <v>0.11192669751261211</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -936,58 +936,58 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>9.999999999999995E-3</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>1.2857142857142853E-2</v>
+        <v>1.0000000000000005E-2</v>
       </c>
       <c r="G3">
-        <v>1.5714285714285712E-2</v>
+        <v>1.5132142463290053E-2</v>
       </c>
       <c r="H3">
-        <v>1.8571428571428569E-2</v>
+        <v>2.0264284926580101E-2</v>
       </c>
       <c r="I3">
-        <v>2.1428571428571425E-2</v>
+        <v>2.5396427389870149E-2</v>
       </c>
       <c r="J3">
-        <v>2.4285714285714285E-2</v>
+        <v>3.0528569853160197E-2</v>
       </c>
       <c r="K3">
-        <v>2.7142857142857142E-2</v>
+        <v>3.5660712316450245E-2</v>
       </c>
       <c r="L3">
-        <v>0.03</v>
+        <v>4.079285477974029E-2</v>
       </c>
       <c r="M3">
-        <v>3.2857142857142856E-2</v>
+        <v>4.5924997243030341E-2</v>
       </c>
       <c r="N3">
-        <v>3.5714285714285712E-2</v>
+        <v>5.1057139706320392E-2</v>
       </c>
       <c r="O3">
-        <v>3.8571428571428569E-2</v>
+        <v>5.6189282169610437E-2</v>
       </c>
       <c r="P3">
-        <v>4.1428571428571433E-2</v>
+        <v>6.1321424632900481E-2</v>
       </c>
       <c r="Q3">
-        <v>4.4285714285714289E-2</v>
+        <v>6.6453567096190533E-2</v>
       </c>
       <c r="R3">
-        <v>4.7142857142857146E-2</v>
+        <v>7.1585709559480584E-2</v>
       </c>
       <c r="S3">
-        <v>0.05</v>
+        <v>7.6717852022770622E-2</v>
       </c>
       <c r="T3">
-        <v>5.2857142857142859E-2</v>
+        <v>8.1849994486060673E-2</v>
       </c>
       <c r="U3">
-        <v>5.5714285714285716E-2</v>
+        <v>8.6982136949350725E-2</v>
       </c>
       <c r="V3">
-        <v>5.8571428571428573E-2</v>
+        <v>9.2114279412640776E-2</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -1004,58 +1004,58 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>9.9999999999999985E-3</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>1.4285714285714285E-2</v>
+        <v>0.49999999999999989</v>
       </c>
       <c r="G4">
-        <v>1.8571428571428572E-2</v>
+        <v>0.59057845609524617</v>
       </c>
       <c r="H4">
-        <v>2.2857142857142857E-2</v>
+        <v>0.68115691219049257</v>
       </c>
       <c r="I4">
-        <v>2.7142857142857142E-2</v>
+        <v>0.77173536828573885</v>
       </c>
       <c r="J4">
-        <v>3.1428571428571431E-2</v>
+        <v>0.86231382438098514</v>
       </c>
       <c r="K4">
-        <v>3.5714285714285712E-2</v>
+        <v>0.95289228047623142</v>
       </c>
       <c r="L4">
-        <v>0.04</v>
+        <v>1.0434707365714777</v>
       </c>
       <c r="M4">
-        <v>4.4285714285714289E-2</v>
+        <v>1.134049192666724</v>
       </c>
       <c r="N4">
-        <v>4.8571428571428571E-2</v>
+        <v>1.2246276487619703</v>
       </c>
       <c r="O4">
-        <v>5.2857142857142859E-2</v>
+        <v>1.3152061048572166</v>
       </c>
       <c r="P4">
-        <v>5.7142857142857148E-2</v>
+        <v>1.4057845609524628</v>
       </c>
       <c r="Q4">
-        <v>6.142857142857143E-2</v>
+        <v>1.4963630170477091</v>
       </c>
       <c r="R4">
-        <v>6.5714285714285725E-2</v>
+        <v>1.5869414731429554</v>
       </c>
       <c r="S4">
-        <v>7.0000000000000007E-2</v>
+        <v>1.6775199292382017</v>
       </c>
       <c r="T4">
-        <v>7.4285714285714288E-2</v>
+        <v>1.768098385333448</v>
       </c>
       <c r="U4">
-        <v>7.857142857142857E-2</v>
+        <v>1.8586768414286943</v>
       </c>
       <c r="V4">
-        <v>8.2857142857142865E-2</v>
+        <v>1.9492552975239406</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
@@ -1072,58 +1072,58 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>9.9999999999999933E-3</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>1.3809523809523803E-2</v>
+        <v>0.49999999999999989</v>
       </c>
       <c r="G5">
-        <v>1.7619047619047611E-2</v>
+        <v>0.59057845609524617</v>
       </c>
       <c r="H5">
-        <v>2.1428571428571422E-2</v>
+        <v>0.68115691219049257</v>
       </c>
       <c r="I5">
-        <v>2.5238095238095233E-2</v>
+        <v>0.77173536828573885</v>
       </c>
       <c r="J5">
-        <v>2.9047619047619041E-2</v>
+        <v>0.86231382438098514</v>
       </c>
       <c r="K5">
-        <v>3.2857142857142849E-2</v>
+        <v>0.95289228047623142</v>
       </c>
       <c r="L5">
-        <v>3.666666666666666E-2</v>
+        <v>1.0434707365714777</v>
       </c>
       <c r="M5">
-        <v>4.0476190476190471E-2</v>
+        <v>1.134049192666724</v>
       </c>
       <c r="N5">
-        <v>4.4285714285714282E-2</v>
+        <v>1.2246276487619703</v>
       </c>
       <c r="O5">
-        <v>4.8095238095238087E-2</v>
+        <v>1.3152061048572166</v>
       </c>
       <c r="P5">
-        <v>5.1904761904761898E-2</v>
+        <v>1.4057845609524628</v>
       </c>
       <c r="Q5">
-        <v>5.5714285714285709E-2</v>
+        <v>1.4963630170477091</v>
       </c>
       <c r="R5">
-        <v>5.9523809523809514E-2</v>
+        <v>1.5869414731429554</v>
       </c>
       <c r="S5">
-        <v>6.3333333333333325E-2</v>
+        <v>1.6775199292382017</v>
       </c>
       <c r="T5">
-        <v>6.7142857142857143E-2</v>
+        <v>1.768098385333448</v>
       </c>
       <c r="U5">
-        <v>7.0952380952380933E-2</v>
+        <v>1.8586768414286943</v>
       </c>
       <c r="V5">
-        <v>7.4761904761904752E-2</v>
+        <v>1.9492552975239406</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
@@ -1140,58 +1140,58 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>9.9999999999999933E-3</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>1.3809523809523803E-2</v>
+        <v>0.49999999999999989</v>
       </c>
       <c r="G6">
-        <v>1.7619047619047611E-2</v>
+        <v>0.59057845609524617</v>
       </c>
       <c r="H6">
-        <v>2.1428571428571422E-2</v>
+        <v>0.68115691219049257</v>
       </c>
       <c r="I6">
-        <v>2.5238095238095233E-2</v>
+        <v>0.77173536828573885</v>
       </c>
       <c r="J6">
-        <v>2.9047619047619041E-2</v>
+        <v>0.86231382438098514</v>
       </c>
       <c r="K6">
-        <v>3.2857142857142849E-2</v>
+        <v>0.95289228047623142</v>
       </c>
       <c r="L6">
-        <v>3.666666666666666E-2</v>
+        <v>1.0434707365714777</v>
       </c>
       <c r="M6">
-        <v>4.0476190476190471E-2</v>
+        <v>1.134049192666724</v>
       </c>
       <c r="N6">
-        <v>4.4285714285714282E-2</v>
+        <v>1.2246276487619703</v>
       </c>
       <c r="O6">
-        <v>4.8095238095238087E-2</v>
+        <v>1.3152061048572166</v>
       </c>
       <c r="P6">
-        <v>5.1904761904761898E-2</v>
+        <v>1.4057845609524628</v>
       </c>
       <c r="Q6">
-        <v>5.5714285714285709E-2</v>
+        <v>1.4963630170477091</v>
       </c>
       <c r="R6">
-        <v>5.9523809523809514E-2</v>
+        <v>1.5869414731429554</v>
       </c>
       <c r="S6">
-        <v>6.3333333333333325E-2</v>
+        <v>1.6775199292382017</v>
       </c>
       <c r="T6">
-        <v>6.7142857142857143E-2</v>
+        <v>1.768098385333448</v>
       </c>
       <c r="U6">
-        <v>7.0952380952380933E-2</v>
+        <v>1.8586768414286943</v>
       </c>
       <c r="V6">
-        <v>7.4761904761904752E-2</v>
+        <v>1.9492552975239406</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
@@ -1208,58 +1208,58 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>9.9999999999999933E-3</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>1.3809523809523803E-2</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>1.7619047619047611E-2</v>
+        <v>0.10000000000000007</v>
       </c>
       <c r="H7">
-        <v>2.1428571428571422E-2</v>
+        <v>0.13402561270371591</v>
       </c>
       <c r="I7">
-        <v>2.5238095238095233E-2</v>
+        <v>0.16805122540743173</v>
       </c>
       <c r="J7">
-        <v>2.9047619047619041E-2</v>
+        <v>0.20207683811114757</v>
       </c>
       <c r="K7">
-        <v>3.2857142857142849E-2</v>
+        <v>0.23610245081486342</v>
       </c>
       <c r="L7">
-        <v>3.666666666666666E-2</v>
+        <v>0.27012806351857921</v>
       </c>
       <c r="M7">
-        <v>4.0476190476190471E-2</v>
+        <v>0.30415367622229506</v>
       </c>
       <c r="N7">
-        <v>4.4285714285714282E-2</v>
+        <v>0.3381792889260109</v>
       </c>
       <c r="O7">
-        <v>4.8095238095238087E-2</v>
+        <v>0.37220490162972675</v>
       </c>
       <c r="P7">
-        <v>5.1904761904761898E-2</v>
+        <v>0.40623051433344259</v>
       </c>
       <c r="Q7">
-        <v>5.5714285714285709E-2</v>
+        <v>0.44025612703715838</v>
       </c>
       <c r="R7">
-        <v>5.9523809523809514E-2</v>
+        <v>0.47428173974087423</v>
       </c>
       <c r="S7">
-        <v>6.3333333333333325E-2</v>
+        <v>0.50830735244459002</v>
       </c>
       <c r="T7">
-        <v>6.7142857142857143E-2</v>
+        <v>0.54233296514830587</v>
       </c>
       <c r="U7">
-        <v>7.0952380952380933E-2</v>
+        <v>0.57635857785202171</v>
       </c>
       <c r="V7">
-        <v>7.4761904761904752E-2</v>
+        <v>0.61038419055573756</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
@@ -1276,58 +1276,58 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>2.0948616600790287E-3</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>7.5663466967814588E-3</v>
+        <v>0.49999999999999989</v>
       </c>
       <c r="G8">
-        <v>1.3037831733483888E-2</v>
+        <v>0.59057845609524617</v>
       </c>
       <c r="H8">
-        <v>1.8509316770186319E-2</v>
+        <v>0.68115691219049257</v>
       </c>
       <c r="I8">
-        <v>2.398080180688875E-2</v>
+        <v>0.77173536828573885</v>
       </c>
       <c r="J8">
-        <v>2.9452286843591177E-2</v>
+        <v>0.86231382438098514</v>
       </c>
       <c r="K8">
-        <v>3.4923771880293608E-2</v>
+        <v>0.95289228047623142</v>
       </c>
       <c r="L8">
-        <v>4.0395256916996039E-2</v>
+        <v>1.0434707365714777</v>
       </c>
       <c r="M8">
-        <v>4.586674195369847E-2</v>
+        <v>1.134049192666724</v>
       </c>
       <c r="N8">
-        <v>5.1338226990400901E-2</v>
+        <v>1.2246276487619703</v>
       </c>
       <c r="O8">
-        <v>5.6809712027103332E-2</v>
+        <v>1.3152061048572166</v>
       </c>
       <c r="P8">
-        <v>6.2281197063805756E-2</v>
+        <v>1.4057845609524628</v>
       </c>
       <c r="Q8">
-        <v>6.7752682100508194E-2</v>
+        <v>1.4963630170477091</v>
       </c>
       <c r="R8">
-        <v>7.3224167137210611E-2</v>
+        <v>1.5869414731429554</v>
       </c>
       <c r="S8">
-        <v>7.8695652173913055E-2</v>
+        <v>1.6775199292382017</v>
       </c>
       <c r="T8">
-        <v>8.4167137210615472E-2</v>
+        <v>1.768098385333448</v>
       </c>
       <c r="U8">
-        <v>8.9638622247317917E-2</v>
+        <v>1.8586768414286943</v>
       </c>
       <c r="V8">
-        <v>9.5110107284020334E-2</v>
+        <v>1.9492552975239406</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
@@ -1350,52 +1350,52 @@
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>5.000000000000001E-2</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>6.7268655483123621E-2</v>
       </c>
       <c r="I9">
-        <v>5.000000000000001E-2</v>
+        <v>8.4537310966247226E-2</v>
       </c>
       <c r="J9">
-        <v>5.6470588235294127E-2</v>
+        <v>0.10180596644937084</v>
       </c>
       <c r="K9">
-        <v>6.294117647058825E-2</v>
+        <v>0.11907462193249446</v>
       </c>
       <c r="L9">
-        <v>6.9411764705882367E-2</v>
+        <v>0.13634327741561808</v>
       </c>
       <c r="M9">
-        <v>7.5882352941176484E-2</v>
+        <v>0.15361193289874167</v>
       </c>
       <c r="N9">
-        <v>8.2352941176470601E-2</v>
+        <v>0.17088058838186529</v>
       </c>
       <c r="O9">
-        <v>8.8823529411764718E-2</v>
+        <v>0.18814924386498891</v>
       </c>
       <c r="P9">
-        <v>9.5294117647058835E-2</v>
+        <v>0.20541789934811253</v>
       </c>
       <c r="Q9">
-        <v>0.10176470588235295</v>
+        <v>0.22268655483123612</v>
       </c>
       <c r="R9">
-        <v>0.10823529411764707</v>
+        <v>0.23995521031435973</v>
       </c>
       <c r="S9">
-        <v>0.11470588235294119</v>
+        <v>0.25722386579748335</v>
       </c>
       <c r="T9">
-        <v>0.1211764705882353</v>
+        <v>0.27449252128060697</v>
       </c>
       <c r="U9">
-        <v>0.12764705882352942</v>
+        <v>0.29176117676373059</v>
       </c>
       <c r="V9">
-        <v>0.13411764705882354</v>
+        <v>0.30902983224685421</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
@@ -1406,64 +1406,64 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>1.0000000000000005E-2</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>1.3913043478260874E-2</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>1.7826086956521742E-2</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>2.1739130434782612E-2</v>
+        <v>0.05</v>
       </c>
       <c r="G10">
-        <v>2.5652173913043481E-2</v>
+        <v>7.2904209270023085E-2</v>
       </c>
       <c r="H10">
-        <v>2.9565217391304348E-2</v>
+        <v>9.5808418540046153E-2</v>
       </c>
       <c r="I10">
-        <v>3.3478260869565221E-2</v>
+        <v>0.11871262781006924</v>
       </c>
       <c r="J10">
-        <v>3.7391304347826088E-2</v>
+        <v>0.14161683708009232</v>
       </c>
       <c r="K10">
-        <v>4.1304347826086954E-2</v>
+        <v>0.16452104635011539</v>
       </c>
       <c r="L10">
-        <v>4.5217391304347827E-2</v>
+        <v>0.18742525562013848</v>
       </c>
       <c r="M10">
-        <v>4.9130434782608694E-2</v>
+        <v>0.21032946489016155</v>
       </c>
       <c r="N10">
-        <v>5.304347826086956E-2</v>
+        <v>0.23323367416018462</v>
       </c>
       <c r="O10">
-        <v>5.6956521739130433E-2</v>
+        <v>0.25613788343020771</v>
       </c>
       <c r="P10">
-        <v>6.08695652173913E-2</v>
+        <v>0.27904209270023078</v>
       </c>
       <c r="Q10">
-        <v>6.4782608695652166E-2</v>
+        <v>0.30194630197025385</v>
       </c>
       <c r="R10">
-        <v>6.8695652173913047E-2</v>
+        <v>0.32485051124027692</v>
       </c>
       <c r="S10">
-        <v>7.2608695652173899E-2</v>
+        <v>0.34775472051030004</v>
       </c>
       <c r="T10">
-        <v>7.6521739130434779E-2</v>
+        <v>0.37065892978032311</v>
       </c>
       <c r="U10">
-        <v>8.043478260869566E-2</v>
+        <v>0.39356313905034618</v>
       </c>
       <c r="V10">
-        <v>8.4347826086956512E-2</v>
+        <v>0.41646734832036925</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
@@ -1480,58 +1480,58 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>6.1904761904761907E-2</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>7.3809523809523811E-2</v>
+        <v>0.50000000000000022</v>
       </c>
       <c r="H11">
-        <v>8.5714285714285715E-2</v>
+        <v>0.67925244592324585</v>
       </c>
       <c r="I11">
-        <v>9.7619047619047619E-2</v>
+        <v>0.85850489184649137</v>
       </c>
       <c r="J11">
-        <v>0.10952380952380952</v>
+        <v>1.0377573377697371</v>
       </c>
       <c r="K11">
-        <v>0.12142857142857143</v>
+        <v>1.2170097836929825</v>
       </c>
       <c r="L11">
-        <v>0.13333333333333333</v>
+        <v>1.3962622296162281</v>
       </c>
       <c r="M11">
-        <v>0.14523809523809522</v>
+        <v>1.5755146755394738</v>
       </c>
       <c r="N11">
-        <v>0.15714285714285714</v>
+        <v>1.7547671214627194</v>
       </c>
       <c r="O11">
-        <v>0.16904761904761903</v>
+        <v>1.934019567385965</v>
       </c>
       <c r="P11">
-        <v>0.18095238095238095</v>
+        <v>2.1132720133092109</v>
       </c>
       <c r="Q11">
-        <v>0.19285714285714287</v>
+        <v>2.2925244592324563</v>
       </c>
       <c r="R11">
-        <v>0.20476190476190476</v>
+        <v>2.4717769051557017</v>
       </c>
       <c r="S11">
-        <v>0.21666666666666665</v>
+        <v>2.6510293510789475</v>
       </c>
       <c r="T11">
-        <v>0.22857142857142856</v>
+        <v>2.830281797002193</v>
       </c>
       <c r="U11">
-        <v>0.24047619047619048</v>
+        <v>3.0095342429254388</v>
       </c>
       <c r="V11">
-        <v>0.25238095238095237</v>
+        <v>3.1887866888486842</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
@@ -1548,58 +1548,58 @@
         <v>0</v>
       </c>
       <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
         <v>0.05</v>
       </c>
-      <c r="F12">
-        <v>6.1904761904761907E-2</v>
-      </c>
-      <c r="G12">
-        <v>7.3809523809523811E-2</v>
-      </c>
       <c r="H12">
-        <v>8.5714285714285715E-2</v>
+        <v>6.8386100746280071E-2</v>
       </c>
       <c r="I12">
-        <v>9.7619047619047619E-2</v>
+        <v>8.6772201492560153E-2</v>
       </c>
       <c r="J12">
-        <v>0.10952380952380952</v>
+        <v>0.10515830223884022</v>
       </c>
       <c r="K12">
-        <v>0.12142857142857143</v>
+        <v>0.12354440298512029</v>
       </c>
       <c r="L12">
-        <v>0.13333333333333333</v>
+        <v>0.14193050373140037</v>
       </c>
       <c r="M12">
-        <v>0.14523809523809522</v>
+        <v>0.16031660447768042</v>
       </c>
       <c r="N12">
-        <v>0.15714285714285714</v>
+        <v>0.17870270522396051</v>
       </c>
       <c r="O12">
-        <v>0.16904761904761903</v>
+        <v>0.19708880597024059</v>
       </c>
       <c r="P12">
-        <v>0.18095238095238095</v>
+        <v>0.21547490671652064</v>
       </c>
       <c r="Q12">
-        <v>0.19285714285714287</v>
+        <v>0.23386100746280072</v>
       </c>
       <c r="R12">
-        <v>0.20476190476190476</v>
+        <v>0.25224710820908081</v>
       </c>
       <c r="S12">
-        <v>0.21666666666666665</v>
+        <v>0.27063320895536086</v>
       </c>
       <c r="T12">
-        <v>0.22857142857142856</v>
+        <v>0.28901930970164091</v>
       </c>
       <c r="U12">
-        <v>0.24047619047619048</v>
+        <v>0.30740541044792102</v>
       </c>
       <c r="V12">
-        <v>0.25238095238095237</v>
+        <v>0.32579151119420108</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
@@ -1619,55 +1619,55 @@
         <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
+        <v>4.9999999999999774E-2</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>0.1014396831052017</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>0.15287936621040363</v>
       </c>
       <c r="I13">
-        <v>4.9999999999999947E-2</v>
+        <v>0.20431904931560554</v>
       </c>
       <c r="J13">
-        <v>5.8823529411764656E-2</v>
+        <v>0.25575873242080749</v>
       </c>
       <c r="K13">
-        <v>6.7647058823529366E-2</v>
+        <v>0.30719841552600941</v>
       </c>
       <c r="L13">
-        <v>7.6470588235294082E-2</v>
+        <v>0.35863809863121132</v>
       </c>
       <c r="M13">
-        <v>8.5294117647058798E-2</v>
+        <v>0.41007778173641324</v>
       </c>
       <c r="N13">
-        <v>9.41176470588235E-2</v>
+        <v>0.46151746484161515</v>
       </c>
       <c r="O13">
-        <v>0.10294117647058822</v>
+        <v>0.51295714794681713</v>
       </c>
       <c r="P13">
-        <v>0.11176470588235293</v>
+        <v>0.56439683105201899</v>
       </c>
       <c r="Q13">
-        <v>0.12058823529411765</v>
+        <v>0.61583651415722096</v>
       </c>
       <c r="R13">
-        <v>0.12941176470588237</v>
+        <v>0.66727619726242282</v>
       </c>
       <c r="S13">
-        <v>0.13823529411764707</v>
+        <v>0.71871588036762479</v>
       </c>
       <c r="T13">
-        <v>0.1470588235294118</v>
+        <v>0.77015556347282665</v>
       </c>
       <c r="U13">
-        <v>0.1558823529411765</v>
+        <v>0.82159524657802863</v>
       </c>
       <c r="V13">
-        <v>0.1647058823529412</v>
+        <v>0.8730349296832306</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
@@ -1696,46 +1696,46 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>9.9999999999999395E-3</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>2.1176470588235241E-2</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>3.2352941176470543E-2</v>
+        <v>0</v>
       </c>
       <c r="L14">
-        <v>4.3529411764705844E-2</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>5.4705882352941146E-2</v>
+        <v>0</v>
       </c>
       <c r="N14">
-        <v>6.5882352941176447E-2</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>7.7058823529411749E-2</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>8.8235294117647051E-2</v>
+        <v>0</v>
       </c>
       <c r="Q14">
-        <v>9.9411764705882352E-2</v>
+        <v>0</v>
       </c>
       <c r="R14">
-        <v>0.11058823529411765</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>0.12176470588235296</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>0.13294117647058826</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>0.14411764705882354</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>0.15529411764705886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
@@ -1977,37 +1977,37 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0.10000000000000003</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>0.10714285714285718</v>
+        <v>0</v>
       </c>
       <c r="N18">
-        <v>0.11428571428571432</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>0.12142857142857146</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>0.12857142857142861</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>0.13571428571428573</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>0.14285714285714288</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>0.15714285714285717</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>0.16428571428571431</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>0.17142857142857146</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.3">
@@ -2030,52 +2030,52 @@
         <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>1.000000000000003E-2</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>3.0583058439489316E-2</v>
       </c>
       <c r="I19" s="1">
-        <v>0</v>
+        <v>5.1166116878978603E-2</v>
       </c>
       <c r="J19" s="1">
-        <v>0</v>
+        <v>7.1749175318467889E-2</v>
       </c>
       <c r="K19" s="1">
-        <v>0</v>
+        <v>9.2332233757957183E-2</v>
       </c>
       <c r="L19">
-        <v>1.0000000000000009E-2</v>
+        <v>0.11291529219744646</v>
       </c>
       <c r="M19">
-        <v>3.0714285714285722E-2</v>
+        <v>0.13349835063693574</v>
       </c>
       <c r="N19">
-        <v>5.1428571428571435E-2</v>
+        <v>0.15408140907642504</v>
       </c>
       <c r="O19">
-        <v>7.2142857142857147E-2</v>
+        <v>0.17466446751591433</v>
       </c>
       <c r="P19">
-        <v>9.285714285714286E-2</v>
+        <v>0.19524752595540362</v>
       </c>
       <c r="Q19">
-        <v>0.11357142857142857</v>
+        <v>0.21583058439489289</v>
       </c>
       <c r="R19">
-        <v>0.13428571428571429</v>
+        <v>0.23641364283438218</v>
       </c>
       <c r="S19">
-        <v>0.155</v>
+        <v>0.25699670127387148</v>
       </c>
       <c r="T19">
-        <v>0.17571428571428571</v>
+        <v>0.27757975971336074</v>
       </c>
       <c r="U19">
-        <v>0.19642857142857142</v>
+        <v>0.29816281815285006</v>
       </c>
       <c r="V19">
-        <v>0.21714285714285714</v>
+        <v>0.31874587659233933</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.3">
@@ -2098,52 +2098,52 @@
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>5.0000000000000086E-2</v>
       </c>
       <c r="H20" s="1">
-        <v>0</v>
+        <v>0.10569835705676475</v>
       </c>
       <c r="I20" s="1">
-        <v>0</v>
+        <v>0.1613967141135294</v>
       </c>
       <c r="J20" s="1">
-        <v>0</v>
+        <v>0.21709507117029408</v>
       </c>
       <c r="K20" s="1">
-        <v>0</v>
+        <v>0.27279342822705877</v>
       </c>
       <c r="L20" s="1">
-        <v>0</v>
+        <v>0.32849178528382339</v>
       </c>
       <c r="M20" s="1">
-        <v>0</v>
+        <v>0.38419014234058807</v>
       </c>
       <c r="N20" s="1">
-        <v>0</v>
+        <v>0.43988849939735275</v>
       </c>
       <c r="O20" s="1">
-        <v>0</v>
+        <v>0.49558685645411737</v>
       </c>
       <c r="P20" s="1">
-        <v>0</v>
+        <v>0.55128521351088211</v>
       </c>
       <c r="Q20" s="1">
-        <v>0</v>
+        <v>0.60698357056764674</v>
       </c>
       <c r="R20" s="1">
-        <v>0</v>
+        <v>0.66268192762441136</v>
       </c>
       <c r="S20" s="1">
-        <v>0</v>
+        <v>0.7183802846811761</v>
       </c>
       <c r="T20" s="1">
-        <v>0</v>
+        <v>0.77407864173794072</v>
       </c>
       <c r="U20" s="1">
-        <v>0</v>
+        <v>0.82977699879470546</v>
       </c>
       <c r="V20" s="1">
-        <v>0</v>
+        <v>0.88547535585147008</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
@@ -2163,55 +2163,55 @@
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>0.57036627015174224</v>
       </c>
       <c r="H21" s="1">
-        <v>0</v>
+        <v>0.64073254030348437</v>
       </c>
       <c r="I21" s="1">
-        <v>0</v>
+        <v>0.71109881045522649</v>
       </c>
       <c r="J21" s="1">
-        <v>0</v>
+        <v>0.78146508060696862</v>
       </c>
       <c r="K21" s="1">
-        <v>0</v>
+        <v>0.85183135075871075</v>
       </c>
       <c r="L21" s="1">
-        <v>0</v>
+        <v>0.92219762091045299</v>
       </c>
       <c r="M21" s="1">
-        <v>0</v>
+        <v>0.99256389106219511</v>
       </c>
       <c r="N21" s="1">
-        <v>0</v>
+        <v>1.0629301612139372</v>
       </c>
       <c r="O21" s="1">
-        <v>0</v>
+        <v>1.1332964313656793</v>
       </c>
       <c r="P21" s="1">
-        <v>0</v>
+        <v>1.2036627015174215</v>
       </c>
       <c r="Q21" s="1">
-        <v>0</v>
+        <v>1.2740289716691637</v>
       </c>
       <c r="R21" s="1">
-        <v>0</v>
+        <v>1.344395241820906</v>
       </c>
       <c r="S21" s="1">
-        <v>0</v>
+        <v>1.4147615119726482</v>
       </c>
       <c r="T21" s="1">
-        <v>0</v>
+        <v>1.48512778212439</v>
       </c>
       <c r="U21" s="1">
-        <v>0</v>
+        <v>1.5554940522761322</v>
       </c>
       <c r="V21" s="1">
-        <v>0</v>
+        <v>1.6258603224278745</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.3">
@@ -2231,55 +2231,55 @@
         <v>0</v>
       </c>
       <c r="F22" s="1">
-        <v>0</v>
+        <v>4.9999999999999795E-2</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>9.6966952380721227E-2</v>
       </c>
       <c r="H22" s="1">
-        <v>0</v>
+        <v>0.14393390476144266</v>
       </c>
       <c r="I22" s="1">
-        <v>0</v>
+        <v>0.19090085714216409</v>
       </c>
       <c r="J22" s="1">
-        <v>0</v>
+        <v>0.23786780952288553</v>
       </c>
       <c r="K22" s="1">
-        <v>0</v>
+        <v>0.28483476190360696</v>
       </c>
       <c r="L22" s="1">
-        <v>0</v>
+        <v>0.33180171428432836</v>
       </c>
       <c r="M22" s="1">
-        <v>0</v>
+        <v>0.37876866666504982</v>
       </c>
       <c r="N22" s="1">
-        <v>0</v>
+        <v>0.42573561904577129</v>
       </c>
       <c r="O22" s="1">
-        <v>0</v>
+        <v>0.47270257142649269</v>
       </c>
       <c r="P22" s="1">
-        <v>0</v>
+        <v>0.5196695238072141</v>
       </c>
       <c r="Q22" s="1">
-        <v>0</v>
+        <v>0.56663647618793556</v>
       </c>
       <c r="R22" s="1">
-        <v>0</v>
+        <v>0.61360342856865702</v>
       </c>
       <c r="S22" s="1">
-        <v>0</v>
+        <v>0.66057038094937837</v>
       </c>
       <c r="T22" s="1">
-        <v>0</v>
+        <v>0.70753733333009983</v>
       </c>
       <c r="U22" s="1">
-        <v>0</v>
+        <v>0.75450428571082129</v>
       </c>
       <c r="V22" s="1">
-        <v>0</v>
+        <v>0.80147123809154275</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
@@ -2299,55 +2299,55 @@
         <v>0</v>
       </c>
       <c r="F23" s="1">
-        <v>0</v>
+        <v>5.0000000000000017E-2</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>8.0012069285434084E-2</v>
       </c>
       <c r="H23" s="1">
-        <v>0</v>
+        <v>0.11002413857086814</v>
       </c>
       <c r="I23" s="1">
-        <v>0</v>
+        <v>0.14003620785630222</v>
       </c>
       <c r="J23" s="1">
-        <v>0</v>
+        <v>0.17004827714173626</v>
       </c>
       <c r="K23" s="1">
-        <v>0</v>
+        <v>0.20006034642717033</v>
       </c>
       <c r="L23">
-        <v>9.9999999999999881E-3</v>
+        <v>0.23007241571260439</v>
       </c>
       <c r="M23">
-        <v>2.3571428571428563E-2</v>
+        <v>0.26008448499803849</v>
       </c>
       <c r="N23">
-        <v>3.7142857142857137E-2</v>
+        <v>0.29009655428347253</v>
       </c>
       <c r="O23">
-        <v>5.0714285714285712E-2</v>
+        <v>0.32010862356890657</v>
       </c>
       <c r="P23">
-        <v>6.4285714285714279E-2</v>
+        <v>0.35012069285434066</v>
       </c>
       <c r="Q23">
-        <v>7.7857142857142861E-2</v>
+        <v>0.3801327621397747</v>
       </c>
       <c r="R23">
-        <v>9.1428571428571442E-2</v>
+        <v>0.4101448314252088</v>
       </c>
       <c r="S23">
-        <v>0.10500000000000001</v>
+        <v>0.44015690071064284</v>
       </c>
       <c r="T23">
-        <v>0.11857142857142858</v>
+        <v>0.47016896999607694</v>
       </c>
       <c r="U23">
-        <v>0.13214285714285715</v>
+        <v>0.50018103928151092</v>
       </c>
       <c r="V23">
-        <v>0.14571428571428574</v>
+        <v>0.53019310856694501</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.3">

--- a/SType2.xlsx
+++ b/SType2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-PADAGIMO-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{1A41342C-B3F5-4A60-AB0E-0E5127761BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01C40B24-DBFB-467B-AAB6-E287C2A9EDFB}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{1A41342C-B3F5-4A60-AB0E-0E5127761BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C30AEC0A-42BE-430C-97B1-B22E637ED375}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{B0285223-0237-4445-BB2D-68F96528C948}"/>
   </bookViews>
@@ -871,55 +871,55 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>9.9999999999999985E-3</v>
+        <v>3.6613269642034579E-3</v>
       </c>
       <c r="G2">
-        <v>1.6370418594538257E-2</v>
+        <v>3.6613269642034579E-3</v>
       </c>
       <c r="H2">
-        <v>2.2740837189076511E-2</v>
+        <v>3.6613269642034579E-3</v>
       </c>
       <c r="I2">
-        <v>2.9111255783614769E-2</v>
+        <v>3.6613269642034579E-3</v>
       </c>
       <c r="J2">
-        <v>3.5481674378153027E-2</v>
+        <v>3.6613269642034579E-3</v>
       </c>
       <c r="K2">
-        <v>4.1852092972691282E-2</v>
+        <v>1.8657391033386723E-2</v>
       </c>
       <c r="L2">
-        <v>4.8222511567229544E-2</v>
+        <v>1.8657391033386723E-2</v>
       </c>
       <c r="M2">
-        <v>5.4592930161767798E-2</v>
+        <v>1.8657391033386723E-2</v>
       </c>
       <c r="N2">
-        <v>6.0963348756306053E-2</v>
+        <v>1.8657391033386723E-2</v>
       </c>
       <c r="O2">
-        <v>6.7333767350844315E-2</v>
+        <v>1.8657391033386723E-2</v>
       </c>
       <c r="P2">
-        <v>7.3704185945382569E-2</v>
+        <v>4.5230519879391036E-2</v>
       </c>
       <c r="Q2">
-        <v>8.0074604539920824E-2</v>
+        <v>4.5230519879391036E-2</v>
       </c>
       <c r="R2">
-        <v>8.6445023134459079E-2</v>
+        <v>4.5230519879391036E-2</v>
       </c>
       <c r="S2">
-        <v>9.2815441728997347E-2</v>
+        <v>4.5230519879391036E-2</v>
       </c>
       <c r="T2">
-        <v>9.9185860323535602E-2</v>
+        <v>4.5230519879391036E-2</v>
       </c>
       <c r="U2">
-        <v>0.10555627891807386</v>
+        <v>4.5230519879391036E-2</v>
       </c>
       <c r="V2">
-        <v>0.11192669751261211</v>
+        <v>9.240000000000001E-2</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -939,55 +939,55 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>1.0000000000000005E-2</v>
+        <v>5.6653285609760918E-3</v>
       </c>
       <c r="G3">
-        <v>1.5132142463290053E-2</v>
+        <v>5.6653285609760918E-3</v>
       </c>
       <c r="H3">
-        <v>2.0264284926580101E-2</v>
+        <v>5.6653285609760918E-3</v>
       </c>
       <c r="I3">
-        <v>2.5396427389870149E-2</v>
+        <v>5.6653285609760918E-3</v>
       </c>
       <c r="J3">
-        <v>3.0528569853160197E-2</v>
+        <v>5.6653285609760918E-3</v>
       </c>
       <c r="K3">
-        <v>3.5660712316450245E-2</v>
+        <v>1.7357054331872474E-2</v>
       </c>
       <c r="L3">
-        <v>4.079285477974029E-2</v>
+        <v>1.7357054331872474E-2</v>
       </c>
       <c r="M3">
-        <v>4.5924997243030341E-2</v>
+        <v>1.7357054331872474E-2</v>
       </c>
       <c r="N3">
-        <v>5.1057139706320392E-2</v>
+        <v>1.7357054331872474E-2</v>
       </c>
       <c r="O3">
-        <v>5.6189282169610437E-2</v>
+        <v>1.7357054331872474E-2</v>
       </c>
       <c r="P3">
-        <v>6.1321424632900481E-2</v>
+        <v>3.2511767778831344E-2</v>
       </c>
       <c r="Q3">
-        <v>6.6453567096190533E-2</v>
+        <v>3.2511767778831344E-2</v>
       </c>
       <c r="R3">
-        <v>7.1585709559480584E-2</v>
+        <v>3.2511767778831344E-2</v>
       </c>
       <c r="S3">
-        <v>7.6717852022770622E-2</v>
+        <v>3.2511767778831344E-2</v>
       </c>
       <c r="T3">
-        <v>8.1849994486060673E-2</v>
+        <v>3.2511767778831344E-2</v>
       </c>
       <c r="U3">
-        <v>8.6982136949350725E-2</v>
+        <v>3.2511767778831344E-2</v>
       </c>
       <c r="V3">
-        <v>9.2114279412640776E-2</v>
+        <v>5.5268567647584484E-2</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -1007,55 +1007,55 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0.49999999999999989</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>0.59057845609524617</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.68115691219049257</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.77173536828573885</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0.86231382438098514</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>0.95289228047623142</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>1.0434707365714777</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.134049192666724</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>1.2246276487619703</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>1.3152061048572166</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>1.4057845609524628</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>1.4963630170477091</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>1.5869414731429554</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>1.6775199292382017</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>1.768098385333448</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1.8586768414286943</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1.9492552975239406</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
@@ -1075,55 +1075,55 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0.49999999999999989</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>0.59057845609524617</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>0.68115691219049257</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>0.77173536828573885</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0.86231382438098514</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>0.95289228047623142</v>
+        <v>0</v>
       </c>
       <c r="L5">
-        <v>1.0434707365714777</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>1.134049192666724</v>
+        <v>0</v>
       </c>
       <c r="N5">
-        <v>1.2246276487619703</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>1.3152061048572166</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>1.4057845609524628</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.4963630170477091</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>1.5869414731429554</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>1.6775199292382017</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>1.768098385333448</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1.8586768414286943</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>1.9492552975239406</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
@@ -1143,55 +1143,55 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0.49999999999999989</v>
+        <v>6.6532575801162355E-3</v>
       </c>
       <c r="G6">
-        <v>0.59057845609524617</v>
+        <v>1.6775355470200762E-2</v>
       </c>
       <c r="H6">
-        <v>0.68115691219049257</v>
+        <v>2.890359326577328E-2</v>
       </c>
       <c r="I6">
-        <v>0.77173536828573885</v>
+        <v>4.3037970966833788E-2</v>
       </c>
       <c r="J6">
-        <v>0.86231382438098514</v>
+        <v>5.9178488573382294E-2</v>
       </c>
       <c r="K6">
-        <v>0.95289228047623142</v>
+        <v>7.7325146085418781E-2</v>
       </c>
       <c r="L6">
-        <v>1.0434707365714777</v>
+        <v>9.7477943502943254E-2</v>
       </c>
       <c r="M6">
-        <v>1.134049192666724</v>
+        <v>0.11963688082595574</v>
       </c>
       <c r="N6">
-        <v>1.2246276487619703</v>
+        <v>0.14380195805445622</v>
       </c>
       <c r="O6">
-        <v>1.3152061048572166</v>
+        <v>0.16997317518844465</v>
       </c>
       <c r="P6">
-        <v>1.4057845609524628</v>
+        <v>0.19815053222792109</v>
       </c>
       <c r="Q6">
-        <v>1.4963630170477091</v>
+        <v>0.22833402917288556</v>
       </c>
       <c r="R6">
-        <v>1.5869414731429554</v>
+        <v>0.26052366602333799</v>
       </c>
       <c r="S6">
-        <v>1.6775199292382017</v>
+        <v>0.29471944277927836</v>
       </c>
       <c r="T6">
-        <v>1.768098385333448</v>
+        <v>0.33092135944070677</v>
       </c>
       <c r="U6">
-        <v>1.8586768414286943</v>
+        <v>0.36912941600762322</v>
       </c>
       <c r="V6">
-        <v>1.9492552975239406</v>
+        <v>0.4093436124800276</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
@@ -1214,52 +1214,52 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0.10000000000000007</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>0.13402561270371591</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>0.16805122540743173</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>0.20207683811114757</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>0.23610245081486342</v>
+        <v>1.1863722672938415E-2</v>
       </c>
       <c r="L7">
-        <v>0.27012806351857921</v>
+        <v>2.5158111922585411E-2</v>
       </c>
       <c r="M7">
-        <v>0.30415367622229506</v>
+        <v>4.0858296879515241E-2</v>
       </c>
       <c r="N7">
-        <v>0.3381792889260109</v>
+        <v>5.8964277543727905E-2</v>
       </c>
       <c r="O7">
-        <v>0.37220490162972675</v>
+        <v>7.9476053915223402E-2</v>
       </c>
       <c r="P7">
-        <v>0.40623051433344259</v>
+        <v>0.1023936259940017</v>
       </c>
       <c r="Q7">
-        <v>0.44025612703715838</v>
+        <v>0.12771699378006288</v>
       </c>
       <c r="R7">
-        <v>0.47428173974087423</v>
+        <v>0.15544615727340685</v>
       </c>
       <c r="S7">
-        <v>0.50830735244459002</v>
+        <v>0.18558111647403369</v>
       </c>
       <c r="T7">
-        <v>0.54233296514830587</v>
+        <v>0.21812187138194331</v>
       </c>
       <c r="U7">
-        <v>0.57635857785202171</v>
+        <v>0.25306842199713581</v>
       </c>
       <c r="V7">
-        <v>0.61038419055573756</v>
+        <v>0.29042076831961117</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
@@ -1279,55 +1279,55 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>0.49999999999999989</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>0.59057845609524617</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>0.68115691219049257</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>0.77173536828573885</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>0.86231382438098514</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>0.95289228047623142</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>1.0434707365714777</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>1.134049192666724</v>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>1.2246276487619703</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>1.3152061048572166</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>1.4057845609524628</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.4963630170477091</v>
+        <v>0</v>
       </c>
       <c r="R8">
-        <v>1.5869414731429554</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>1.6775199292382017</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>1.768098385333448</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>1.8586768414286943</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>1.9492552975239406</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
@@ -1350,52 +1350,52 @@
         <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>5.000000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>6.7268655483123621E-2</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>8.4537310966247226E-2</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>0.10180596644937084</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>0.11907462193249446</v>
+        <v>5.5955667747570855E-3</v>
       </c>
       <c r="L9">
-        <v>0.13634327741561808</v>
+        <v>1.0032410819161409E-2</v>
       </c>
       <c r="M9">
-        <v>0.15361193289874167</v>
+        <v>1.5446701954896542E-2</v>
       </c>
       <c r="N9">
-        <v>0.17088058838186529</v>
+        <v>2.1838440181962473E-2</v>
       </c>
       <c r="O9">
-        <v>0.18814924386498891</v>
+        <v>2.9207625500359217E-2</v>
       </c>
       <c r="P9">
-        <v>0.20541789934811253</v>
+        <v>3.755425791008677E-2</v>
       </c>
       <c r="Q9">
-        <v>0.22268655483123612</v>
+        <v>4.6878337411145124E-2</v>
       </c>
       <c r="R9">
-        <v>0.23995521031435973</v>
+        <v>5.7179864003534281E-2</v>
       </c>
       <c r="S9">
-        <v>0.25722386579748335</v>
+        <v>6.8458837687254248E-2</v>
       </c>
       <c r="T9">
-        <v>0.27449252128060697</v>
+        <v>8.0715258462305012E-2</v>
       </c>
       <c r="U9">
-        <v>0.29176117676373059</v>
+        <v>9.3949126328686586E-2</v>
       </c>
       <c r="V9">
-        <v>0.30902983224685421</v>
+        <v>0.10816044128639898</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
@@ -1415,55 +1415,55 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>7.2904209270023085E-2</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>9.5808418540046153E-2</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>0.11871262781006924</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>0.14161683708009232</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>0.16452104635011539</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>0.18742525562013848</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>0.21032946489016155</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>0.23323367416018462</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>0.25613788343020771</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>0.27904209270023078</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>0.30194630197025385</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>0.32485051124027692</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>0.34775472051030004</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>0.37065892978032311</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>0.39356313905034618</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>0.41646734832036925</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
@@ -1483,55 +1483,55 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>8.9669430622039146E-4</v>
       </c>
       <c r="G11">
-        <v>0.50000000000000022</v>
+        <v>9.8918213931540044E-3</v>
       </c>
       <c r="H11">
-        <v>0.67925244592324585</v>
+        <v>2.3609966692142687E-2</v>
       </c>
       <c r="I11">
-        <v>0.85850489184649137</v>
+        <v>4.2051130203186439E-2</v>
       </c>
       <c r="J11">
-        <v>1.0377573377697371</v>
+        <v>6.5215311926285269E-2</v>
       </c>
       <c r="K11">
-        <v>1.2170097836929825</v>
+        <v>9.3102511861439155E-2</v>
       </c>
       <c r="L11">
-        <v>1.3962622296162281</v>
+        <v>0.12571273000864813</v>
       </c>
       <c r="M11">
-        <v>1.5755146755394738</v>
+        <v>0.16304596636791219</v>
       </c>
       <c r="N11">
-        <v>1.7547671214627194</v>
+        <v>0.20510222093923128</v>
       </c>
       <c r="O11">
-        <v>1.934019567385965</v>
+        <v>0.25188149372260549</v>
       </c>
       <c r="P11">
-        <v>2.1132720133092109</v>
+        <v>0.30338378471803473</v>
       </c>
       <c r="Q11">
-        <v>2.2925244592324563</v>
+        <v>0.35960909392551904</v>
       </c>
       <c r="R11">
-        <v>2.4717769051557017</v>
+        <v>0.42055742134505852</v>
       </c>
       <c r="S11">
-        <v>2.6510293510789475</v>
+        <v>0.48622876697665296</v>
       </c>
       <c r="T11">
-        <v>2.830281797002193</v>
+        <v>0.55662313082030246</v>
       </c>
       <c r="U11">
-        <v>3.0095342429254388</v>
+        <v>0.63174051287600708</v>
       </c>
       <c r="V11">
-        <v>3.1887866888486842</v>
+        <v>0.7115809131437667</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
@@ -1551,55 +1551,55 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="G12">
-        <v>0.05</v>
+        <v>6.8750000000000006E-2</v>
       </c>
       <c r="H12">
-        <v>6.8386100746280071E-2</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="I12">
-        <v>8.6772201492560153E-2</v>
+        <v>0.10625</v>
       </c>
       <c r="J12">
-        <v>0.10515830223884022</v>
+        <v>0.125</v>
       </c>
       <c r="K12">
-        <v>0.12354440298512029</v>
+        <v>0.14374999999999999</v>
       </c>
       <c r="L12">
-        <v>0.14193050373140037</v>
+        <v>0.16250000000000001</v>
       </c>
       <c r="M12">
-        <v>0.16031660447768042</v>
+        <v>0.18124999999999999</v>
       </c>
       <c r="N12">
-        <v>0.17870270522396051</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="O12">
-        <v>0.19708880597024059</v>
+        <v>0.21875</v>
       </c>
       <c r="P12">
-        <v>0.21547490671652064</v>
+        <v>0.23749999999999999</v>
       </c>
       <c r="Q12">
-        <v>0.23386100746280072</v>
+        <v>0.25624999999999998</v>
       </c>
       <c r="R12">
-        <v>0.25224710820908081</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="S12">
-        <v>0.27063320895536086</v>
+        <v>0.29375000000000001</v>
       </c>
       <c r="T12">
-        <v>0.28901930970164091</v>
+        <v>0.3125</v>
       </c>
       <c r="U12">
-        <v>0.30740541044792102</v>
+        <v>0.33124999999999999</v>
       </c>
       <c r="V12">
-        <v>0.32579151119420108</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
@@ -1619,55 +1619,55 @@
         <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>4.9999999999999774E-2</v>
+        <v>2.1919050199029296E-3</v>
       </c>
       <c r="G13" s="1">
-        <v>0.1014396831052017</v>
+        <v>5.4182487502950783E-3</v>
       </c>
       <c r="H13" s="1">
-        <v>0.15287936621040363</v>
+        <v>9.7239585684147384E-3</v>
       </c>
       <c r="I13">
-        <v>0.20431904931560554</v>
+        <v>1.5109034474261903E-2</v>
       </c>
       <c r="J13">
-        <v>0.25575873242080749</v>
+        <v>2.157347646783658E-2</v>
       </c>
       <c r="K13">
-        <v>0.30719841552600941</v>
+        <v>2.9117284549138769E-2</v>
       </c>
       <c r="L13">
-        <v>0.35863809863121132</v>
+        <v>3.774045871816846E-2</v>
       </c>
       <c r="M13">
-        <v>0.41007778173641324</v>
+        <v>4.7442998974925661E-2</v>
       </c>
       <c r="N13">
-        <v>0.46151746484161515</v>
+        <v>5.8224905319410374E-2</v>
       </c>
       <c r="O13">
-        <v>0.51295714794681713</v>
+        <v>7.0086177751622597E-2</v>
       </c>
       <c r="P13">
-        <v>0.56439683105201899</v>
+        <v>8.3026816271562304E-2</v>
       </c>
       <c r="Q13">
-        <v>0.61583651415722096</v>
+        <v>9.704682087922957E-2</v>
       </c>
       <c r="R13">
-        <v>0.66727619726242282</v>
+        <v>0.11214619157462431</v>
       </c>
       <c r="S13">
-        <v>0.71871588036762479</v>
+        <v>0.12832492835774656</v>
       </c>
       <c r="T13">
-        <v>0.77015556347282665</v>
+        <v>0.14558303122859634</v>
       </c>
       <c r="U13">
-        <v>0.82159524657802863</v>
+        <v>0.16392050018717358</v>
       </c>
       <c r="V13">
-        <v>0.8730349296832306</v>
+        <v>0.18333733523347837</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
@@ -2027,55 +2027,55 @@
         <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>8.3157894736842122E-3</v>
       </c>
       <c r="G19" s="1">
-        <v>1.000000000000003E-2</v>
+        <v>1.3921821287189684E-2</v>
       </c>
       <c r="H19" s="1">
-        <v>3.0583058439489316E-2</v>
+        <v>2.0942305082760102E-2</v>
       </c>
       <c r="I19" s="1">
-        <v>5.1166116878978603E-2</v>
+        <v>2.9377240860395459E-2</v>
       </c>
       <c r="J19" s="1">
-        <v>7.1749175318467889E-2</v>
+        <v>3.9226628620095766E-2</v>
       </c>
       <c r="K19" s="1">
-        <v>9.2332233757957183E-2</v>
+        <v>5.0490468361861017E-2</v>
       </c>
       <c r="L19">
-        <v>0.11291529219744646</v>
+        <v>6.3168760085691195E-2</v>
       </c>
       <c r="M19">
-        <v>0.13349835063693574</v>
+        <v>7.7261503791586347E-2</v>
       </c>
       <c r="N19">
-        <v>0.15408140907642504</v>
+        <v>9.2768699479546426E-2</v>
       </c>
       <c r="O19">
-        <v>0.17466446751591433</v>
+        <v>0.10969034714957146</v>
       </c>
       <c r="P19">
-        <v>0.19524752595540362</v>
+        <v>0.12802644680166139</v>
       </c>
       <c r="Q19">
-        <v>0.21583058439489289</v>
+        <v>0.14777699843581632</v>
       </c>
       <c r="R19">
-        <v>0.23641364283438218</v>
+        <v>0.16894200205203622</v>
       </c>
       <c r="S19">
-        <v>0.25699670127387148</v>
+        <v>0.191521457650321</v>
       </c>
       <c r="T19">
-        <v>0.27757975971336074</v>
+        <v>0.21551536523067075</v>
       </c>
       <c r="U19">
-        <v>0.29816281815285006</v>
+        <v>0.24092372479308541</v>
       </c>
       <c r="V19">
-        <v>0.31874587659233933</v>
+        <v>0.26774653633756501</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.3">
@@ -2095,55 +2095,55 @@
         <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>0</v>
+        <v>1.702187152604446E-5</v>
       </c>
       <c r="G20" s="1">
-        <v>5.0000000000000086E-2</v>
+        <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>0.10569835705676475</v>
+        <v>0</v>
       </c>
       <c r="I20" s="1">
-        <v>0.1613967141135294</v>
+        <v>0</v>
       </c>
       <c r="J20" s="1">
-        <v>0.21709507117029408</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>0.27279342822705877</v>
+        <v>0</v>
       </c>
       <c r="L20" s="1">
-        <v>0.32849178528382339</v>
+        <v>0</v>
       </c>
       <c r="M20" s="1">
-        <v>0.38419014234058807</v>
+        <v>0</v>
       </c>
       <c r="N20" s="1">
-        <v>0.43988849939735275</v>
+        <v>0</v>
       </c>
       <c r="O20" s="1">
-        <v>0.49558685645411737</v>
+        <v>0</v>
       </c>
       <c r="P20" s="1">
-        <v>0.55128521351088211</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="1">
-        <v>0.60698357056764674</v>
+        <v>0</v>
       </c>
       <c r="R20" s="1">
-        <v>0.66268192762441136</v>
+        <v>0</v>
       </c>
       <c r="S20" s="1">
-        <v>0.7183802846811761</v>
+        <v>0</v>
       </c>
       <c r="T20" s="1">
-        <v>0.77407864173794072</v>
+        <v>0</v>
       </c>
       <c r="U20" s="1">
-        <v>0.82977699879470546</v>
+        <v>0</v>
       </c>
       <c r="V20" s="1">
-        <v>0.88547535585147008</v>
+        <v>3.0991637454801456E-2</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.3">
@@ -2163,55 +2163,55 @@
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>0.5</v>
+        <v>1.9592859855677932E-2</v>
       </c>
       <c r="G21" s="1">
-        <v>0.57036627015174224</v>
+        <v>3.5694657032083875E-2</v>
       </c>
       <c r="H21" s="1">
-        <v>0.64073254030348437</v>
+        <v>5.4228366693253004E-2</v>
       </c>
       <c r="I21" s="1">
-        <v>0.71109881045522649</v>
+        <v>7.5193988839185336E-2</v>
       </c>
       <c r="J21" s="1">
-        <v>0.78146508060696862</v>
+        <v>9.8591523469880857E-2</v>
       </c>
       <c r="K21" s="1">
-        <v>0.85183135075871075</v>
+        <v>0.12442097058533956</v>
       </c>
       <c r="L21" s="1">
-        <v>0.92219762091045299</v>
+        <v>0.15268233018556149</v>
       </c>
       <c r="M21" s="1">
-        <v>0.99256389106219511</v>
+        <v>0.18337560227054658</v>
       </c>
       <c r="N21" s="1">
-        <v>1.0629301612139372</v>
+        <v>0.21650078684029483</v>
       </c>
       <c r="O21" s="1">
-        <v>1.1332964313656793</v>
+        <v>0.25205788389480632</v>
       </c>
       <c r="P21" s="1">
-        <v>1.2036627015174215</v>
+        <v>0.29004689343408097</v>
       </c>
       <c r="Q21" s="1">
-        <v>1.2740289716691637</v>
+        <v>0.33046781545811887</v>
       </c>
       <c r="R21" s="1">
-        <v>1.344395241820906</v>
+        <v>0.37332064996691994</v>
       </c>
       <c r="S21" s="1">
-        <v>1.4147615119726482</v>
+        <v>0.41860539696048421</v>
       </c>
       <c r="T21" s="1">
-        <v>1.48512778212439</v>
+        <v>0.46632205643881164</v>
       </c>
       <c r="U21" s="1">
-        <v>1.5554940522761322</v>
+        <v>0.51647062840190217</v>
       </c>
       <c r="V21" s="1">
-        <v>1.6258603224278745</v>
+        <v>0.56905111284975607</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.3">
@@ -2231,55 +2231,55 @@
         <v>0</v>
       </c>
       <c r="F22" s="1">
-        <v>4.9999999999999795E-2</v>
+        <v>3.7847463902258415E-3</v>
       </c>
       <c r="G22" s="1">
-        <v>9.6966952380721227E-2</v>
+        <v>5.6940739659055413E-3</v>
       </c>
       <c r="H22" s="1">
-        <v>0.14393390476144266</v>
+        <v>7.8182045020499472E-3</v>
       </c>
       <c r="I22" s="1">
-        <v>0.19090085714216409</v>
+        <v>1.0157137998659058E-2</v>
       </c>
       <c r="J22" s="1">
-        <v>0.23786780952288553</v>
+        <v>1.2710874455732874E-2</v>
       </c>
       <c r="K22" s="1">
-        <v>0.28483476190360696</v>
+        <v>1.5479413873271397E-2</v>
       </c>
       <c r="L22" s="1">
-        <v>0.33180171428432836</v>
+        <v>1.8462756251274623E-2</v>
       </c>
       <c r="M22" s="1">
-        <v>0.37876866666504982</v>
+        <v>2.1660901589742557E-2</v>
       </c>
       <c r="N22" s="1">
-        <v>0.42573561904577129</v>
+        <v>2.5073849888675191E-2</v>
       </c>
       <c r="O22" s="1">
-        <v>0.47270257142649269</v>
+        <v>2.8701601148072537E-2</v>
       </c>
       <c r="P22" s="1">
-        <v>0.5196695238072141</v>
+        <v>3.2544155367934584E-2</v>
       </c>
       <c r="Q22" s="1">
-        <v>0.56663647618793556</v>
+        <v>3.6601512548261335E-2</v>
       </c>
       <c r="R22" s="1">
-        <v>0.61360342856865702</v>
+        <v>4.0873672689052794E-2</v>
       </c>
       <c r="S22" s="1">
-        <v>0.66057038094937837</v>
+        <v>4.536063579030896E-2</v>
       </c>
       <c r="T22" s="1">
-        <v>0.70753733333009983</v>
+        <v>5.0062401852029835E-2</v>
       </c>
       <c r="U22" s="1">
-        <v>0.75450428571082129</v>
+        <v>5.4978970874215403E-2</v>
       </c>
       <c r="V22" s="1">
-        <v>0.80147123809154275</v>
+        <v>6.0110342856865687E-2</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.3">
@@ -2299,55 +2299,55 @@
         <v>0</v>
       </c>
       <c r="F23" s="1">
-        <v>5.0000000000000017E-2</v>
+        <v>1.7147271271429933E-3</v>
       </c>
       <c r="G23" s="1">
-        <v>8.0012069285434084E-2</v>
+        <v>4.4885639507063566E-3</v>
       </c>
       <c r="H23" s="1">
-        <v>0.11002413857086814</v>
+        <v>8.4246630383886696E-3</v>
       </c>
       <c r="I23" s="1">
-        <v>0.14003620785630222</v>
+        <v>1.3523024390189931E-2</v>
       </c>
       <c r="J23" s="1">
-        <v>0.17004827714173626</v>
+        <v>1.9783648006110145E-2</v>
       </c>
       <c r="K23" s="1">
-        <v>0.20006034642717033</v>
+        <v>2.7206533886149305E-2</v>
       </c>
       <c r="L23">
-        <v>0.23007241571260439</v>
+        <v>3.5791682030307415E-2</v>
       </c>
       <c r="M23">
-        <v>0.26008448499803849</v>
+        <v>4.5539092438584484E-2</v>
       </c>
       <c r="N23">
-        <v>0.29009655428347253</v>
+        <v>5.6448765110980487E-2</v>
       </c>
       <c r="O23">
-        <v>0.32010862356890657</v>
+        <v>6.8520700047495442E-2</v>
       </c>
       <c r="P23">
-        <v>0.35012069285434066</v>
+        <v>8.1754897248129357E-2</v>
       </c>
       <c r="Q23">
-        <v>0.3801327621397747</v>
+        <v>9.6151356712882219E-2</v>
       </c>
       <c r="R23">
-        <v>0.4101448314252088</v>
+        <v>0.11171007844175404</v>
       </c>
       <c r="S23">
-        <v>0.44015690071064284</v>
+        <v>0.12843106243474478</v>
       </c>
       <c r="T23">
-        <v>0.47016896999607694</v>
+        <v>0.14631430869185449</v>
       </c>
       <c r="U23">
-        <v>0.50018103928151092</v>
+        <v>0.16535981721308315</v>
       </c>
       <c r="V23">
-        <v>0.53019310856694501</v>
+        <v>0.18556758799843079</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.3">

--- a/SType2.xlsx
+++ b/SType2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-PADAGIMO-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{1A41342C-B3F5-4A60-AB0E-0E5127761BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C30AEC0A-42BE-430C-97B1-B22E637ED375}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{1A41342C-B3F5-4A60-AB0E-0E5127761BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13599499-235E-437D-8671-CD77E3D1D46F}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{B0285223-0237-4445-BB2D-68F96528C948}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B0285223-0237-4445-BB2D-68F96528C948}"/>
   </bookViews>
   <sheets>
     <sheet name="SType2" sheetId="1" r:id="rId1"/>
@@ -1146,52 +1146,52 @@
         <v>6.6532575801162355E-3</v>
       </c>
       <c r="G6">
-        <v>1.6775355470200762E-2</v>
+        <v>1.6846715208057722E-2</v>
       </c>
       <c r="H6">
-        <v>2.890359326577328E-2</v>
+        <v>2.9125601339106039E-2</v>
       </c>
       <c r="I6">
-        <v>4.3037970966833788E-2</v>
+        <v>4.3489915973261191E-2</v>
       </c>
       <c r="J6">
-        <v>5.9178488573382294E-2</v>
+        <v>5.993965911052318E-2</v>
       </c>
       <c r="K6">
-        <v>7.7325146085418781E-2</v>
+        <v>7.8474830750891997E-2</v>
       </c>
       <c r="L6">
-        <v>9.7477943502943254E-2</v>
+        <v>9.9095430894367648E-2</v>
       </c>
       <c r="M6">
-        <v>0.11963688082595574</v>
+        <v>0.12180145954095015</v>
       </c>
       <c r="N6">
-        <v>0.14380195805445622</v>
+        <v>0.14659291669063948</v>
       </c>
       <c r="O6">
-        <v>0.16997317518844465</v>
+        <v>0.17346980234343565</v>
       </c>
       <c r="P6">
-        <v>0.19815053222792109</v>
+        <v>0.20243211649933862</v>
       </c>
       <c r="Q6">
-        <v>0.22833402917288556</v>
+        <v>0.23347985915834846</v>
       </c>
       <c r="R6">
-        <v>0.26052366602333799</v>
+        <v>0.26661303032046513</v>
       </c>
       <c r="S6">
-        <v>0.29471944277927836</v>
+        <v>0.30183162998568858</v>
       </c>
       <c r="T6">
-        <v>0.33092135944070677</v>
+        <v>0.33913565815401892</v>
       </c>
       <c r="U6">
-        <v>0.36912941600762322</v>
+        <v>0.37852511482545609</v>
       </c>
       <c r="V6">
-        <v>0.4093436124800276</v>
+        <v>0.4200000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
@@ -1483,55 +1483,55 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>8.9669430622039146E-4</v>
+        <v>7.9996781142309039E-3</v>
       </c>
       <c r="G11">
-        <v>9.8918213931540044E-3</v>
+        <v>1.8060821557551454E-2</v>
       </c>
       <c r="H11">
-        <v>2.3609966692142687E-2</v>
+        <v>3.1973563628408704E-2</v>
       </c>
       <c r="I11">
-        <v>4.2051130203186439E-2</v>
+        <v>4.9737904326802661E-2</v>
       </c>
       <c r="J11">
-        <v>6.5215311926285269E-2</v>
+        <v>7.1353843652733326E-2</v>
       </c>
       <c r="K11">
-        <v>9.3102511861439155E-2</v>
+        <v>9.6821381606200671E-2</v>
       </c>
       <c r="L11">
-        <v>0.12571273000864813</v>
+        <v>0.12614051818720476</v>
       </c>
       <c r="M11">
-        <v>0.16304596636791219</v>
+        <v>0.15931125339574553</v>
       </c>
       <c r="N11">
-        <v>0.20510222093923128</v>
+        <v>0.19633358723182301</v>
       </c>
       <c r="O11">
-        <v>0.25188149372260549</v>
+        <v>0.23720751969543719</v>
       </c>
       <c r="P11">
-        <v>0.30338378471803473</v>
+        <v>0.28193305078658809</v>
       </c>
       <c r="Q11">
-        <v>0.35960909392551904</v>
+        <v>0.33051018050527564</v>
       </c>
       <c r="R11">
-        <v>0.42055742134505852</v>
+        <v>0.38293890885150006</v>
       </c>
       <c r="S11">
-        <v>0.48622876697665296</v>
+        <v>0.4392192358252609</v>
       </c>
       <c r="T11">
-        <v>0.55662313082030246</v>
+        <v>0.49935116142655861</v>
       </c>
       <c r="U11">
-        <v>0.63174051287600708</v>
+        <v>0.56333468565539302</v>
       </c>
       <c r="V11">
-        <v>0.7115809131437667</v>
+        <v>0.63116980851176407</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>2.1919050199029296E-3</v>
+        <v>2.1919050199029318E-3</v>
       </c>
       <c r="G13" s="1">
         <v>5.4182487502950783E-3</v>
@@ -2163,52 +2163,52 @@
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>1.9592859855677932E-2</v>
+        <v>2.073324751689342E-2</v>
       </c>
       <c r="G21" s="1">
-        <v>3.5694657032083875E-2</v>
+        <v>3.7476512752733074E-2</v>
       </c>
       <c r="H21" s="1">
-        <v>5.4228366693253004E-2</v>
+        <v>5.6556658168234616E-2</v>
       </c>
       <c r="I21" s="1">
-        <v>7.5193988839185336E-2</v>
+        <v>7.7973683763398083E-2</v>
       </c>
       <c r="J21" s="1">
-        <v>9.8591523469880857E-2</v>
+        <v>0.10172758953822343</v>
       </c>
       <c r="K21" s="1">
-        <v>0.12442097058533956</v>
+        <v>0.12781837549271069</v>
       </c>
       <c r="L21" s="1">
-        <v>0.15268233018556149</v>
+        <v>0.15624604162685987</v>
       </c>
       <c r="M21" s="1">
-        <v>0.18337560227054658</v>
+        <v>0.18701058794067091</v>
       </c>
       <c r="N21" s="1">
-        <v>0.21650078684029483</v>
+        <v>0.22011201443414388</v>
       </c>
       <c r="O21" s="1">
-        <v>0.25205788389480632</v>
+        <v>0.25555032110727877</v>
       </c>
       <c r="P21" s="1">
-        <v>0.29004689343408097</v>
+        <v>0.2933255079600755</v>
       </c>
       <c r="Q21" s="1">
-        <v>0.33046781545811887</v>
+        <v>0.33343757499253412</v>
       </c>
       <c r="R21" s="1">
-        <v>0.37332064996691994</v>
+        <v>0.37588652220465479</v>
       </c>
       <c r="S21" s="1">
-        <v>0.41860539696048421</v>
+        <v>0.42067234959643723</v>
       </c>
       <c r="T21" s="1">
-        <v>0.46632205643881164</v>
+        <v>0.46779505716788161</v>
       </c>
       <c r="U21" s="1">
-        <v>0.51647062840190217</v>
+        <v>0.51725464491898787</v>
       </c>
       <c r="V21" s="1">
         <v>0.56905111284975607</v>
